--- a/data/trans_orig/P6712-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6712-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo requiere que tenga iniciativa en 2012</t>
+          <t>Población según si su trabajo requiere que tenga iniciativa en 2012 (tasa de respuesta: 99,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8807</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>10478</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>11099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>969</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15545</t>
+          <t>15699</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22882</t>
+          <t>23640</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22147</t>
+          <t>21879</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19291</t>
+          <t>19670</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>40332</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28352</t>
+          <t>28615</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16232</t>
+          <t>15871</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32543</t>
+          <t>33370</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32922</t>
+          <t>33266</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57107</t>
+          <t>57966</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,55%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29648</t>
+          <t>30215</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48526</t>
+          <t>48517</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34940</t>
+          <t>33959</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>52573</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>70693</t>
+          <t>68278</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>97829</t>
+          <t>95301</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13581</t>
+          <t>13661</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32188</t>
+          <t>31242</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27575</t>
+          <t>26241</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26740</t>
+          <t>27665</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>50657</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10374</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27811</t>
+          <t>28830</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16892</t>
+          <t>16341</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16487</t>
+          <t>16645</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37726</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48051</t>
+          <t>48133</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78531</t>
+          <t>78079</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28705</t>
+          <t>28909</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>52827</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83797</t>
+          <t>84337</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120522</t>
+          <t>120984</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73576</t>
+          <t>75848</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107826</t>
+          <t>108869</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55355</t>
+          <t>55008</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87555</t>
+          <t>85599</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141186</t>
+          <t>140719</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182622</t>
+          <t>183655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>172889</t>
+          <t>173093</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>212895</t>
+          <t>211948</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>120364</t>
+          <t>121063</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155615</t>
+          <t>155707</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>306701</t>
+          <t>304806</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>360042</t>
+          <t>355990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,2%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22997</t>
+          <t>22876</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,82 +2110,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>8097</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3954</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>14900</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>21728</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>12935</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>31927</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>1,82%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>8097</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3247</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>15205</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>21728</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>13815</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>33162</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>12292</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31601</t>
+          <t>31610</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21740</t>
+          <t>22680</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22784</t>
+          <t>23365</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46963</t>
+          <t>48383</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58015</t>
+          <t>57985</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>89110</t>
+          <t>88644</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47212</t>
+          <t>48221</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75412</t>
+          <t>76821</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>112755</t>
+          <t>114023</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>154562</t>
+          <t>155583</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88620</t>
+          <t>89651</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>122895</t>
+          <t>124129</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58357</t>
+          <t>59103</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86867</t>
+          <t>87800</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>158925</t>
+          <t>155962</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>205314</t>
+          <t>201317</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>194476</t>
+          <t>192449</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237583</t>
+          <t>234236</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>113440</t>
+          <t>112624</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>148164</t>
+          <t>147382</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>315924</t>
+          <t>317447</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>369095</t>
+          <t>369261</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>28083</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21097</t>
+          <t>22038</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19456</t>
+          <t>19498</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42270</t>
+          <t>41391</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24441</t>
+          <t>23678</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20715</t>
+          <t>20566</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16981</t>
+          <t>17158</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>38887</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39591</t>
+          <t>38064</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>66513</t>
+          <t>67644</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26243</t>
+          <t>26280</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51515</t>
+          <t>51560</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>71432</t>
+          <t>73542</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>111015</t>
+          <t>112300</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,0%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72157</t>
+          <t>70345</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>106436</t>
+          <t>106684</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>46605</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74340</t>
+          <t>76180</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>126095</t>
+          <t>124003</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>172815</t>
+          <t>170450</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>175746</t>
+          <t>174268</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>216097</t>
+          <t>215449</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>86265</t>
+          <t>88579</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>120248</t>
+          <t>119421</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>270531</t>
+          <t>273102</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>322701</t>
+          <t>326732</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>55,29%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>14156</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16776</t>
+          <t>17415</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>15160</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>906</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7925</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18621</t>
+          <t>18082</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14737</t>
+          <t>14891</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33330</t>
+          <t>33781</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19644</t>
+          <t>19673</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>24075</t>
+          <t>24582</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>47676</t>
+          <t>47010</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22016</t>
+          <t>21029</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>42024</t>
+          <t>42281</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>9883</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>25529</t>
+          <t>25886</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>35389</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>60987</t>
+          <t>63565</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>76768</t>
+          <t>76415</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>102051</t>
+          <t>101910</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>27324</t>
+          <t>25721</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>44399</t>
+          <t>43730</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>107361</t>
+          <t>107954</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>141120</t>
+          <t>139328</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>61,65%</t>
         </is>
       </c>
     </row>
@@ -4141,97 +4141,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4367,97 +4367,97 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>44908</t>
+          <t>45490</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>76263</t>
+          <t>75840</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>30812</t>
+          <t>31526</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>56963</t>
+          <t>58312</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>83702</t>
+          <t>84245</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>123871</t>
+          <t>125607</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>50221</t>
+          <t>50751</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>82990</t>
+          <t>85568</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>28392</t>
+          <t>28139</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>55327</t>
+          <t>55068</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>84691</t>
+          <t>85882</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>126713</t>
+          <t>129736</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>198243</t>
+          <t>197806</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>255103</t>
+          <t>253934</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>139925</t>
+          <t>139050</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>187853</t>
+          <t>187434</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>351183</t>
+          <t>348875</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>429729</t>
+          <t>420571</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>297758</t>
+          <t>303730</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>365939</t>
+          <t>370714</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>216212</t>
+          <t>214922</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>277087</t>
+          <t>270920</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>536587</t>
+          <t>535360</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>625118</t>
+          <t>622905</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>695358</t>
+          <t>690323</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>772978</t>
+          <t>768325</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>416587</t>
+          <t>420656</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>482083</t>
+          <t>484486</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1131316</t>
+          <t>1131288</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1232799</t>
+          <t>1235484</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,41%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo requiere que tenga iniciativa en 2016</t>
+          <t>Población según si su trabajo requiere que tenga iniciativa en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>11497</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>13717</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>7359</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21246</t>
+          <t>20981</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18275</t>
+          <t>18352</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15593</t>
+          <t>16237</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33552</t>
+          <t>34328</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10653</t>
+          <t>10551</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26257</t>
+          <t>25910</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14455</t>
+          <t>13927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30656</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27869</t>
+          <t>28841</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50370</t>
+          <t>51036</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18403</t>
+          <t>17622</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34690</t>
+          <t>35143</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16483</t>
+          <t>16978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33400</t>
+          <t>33360</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38305</t>
+          <t>38516</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63192</t>
+          <t>62416</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10849</t>
+          <t>11226</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26433</t>
+          <t>26909</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24542</t>
+          <t>24774</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43532</t>
+          <t>42028</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39001</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63093</t>
+          <t>64411</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,68%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30352</t>
+          <t>30844</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>18201</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22620</t>
+          <t>22481</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45839</t>
+          <t>44540</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23658</t>
+          <t>23791</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45927</t>
+          <t>46528</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17743</t>
+          <t>17156</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36190</t>
+          <t>35907</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46289</t>
+          <t>44874</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74451</t>
+          <t>73817</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59873</t>
+          <t>59864</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>91832</t>
+          <t>90396</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58632</t>
+          <t>58417</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86307</t>
+          <t>87467</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>125676</t>
+          <t>128357</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>168169</t>
+          <t>169407</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73330</t>
+          <t>72895</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105330</t>
+          <t>106100</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61056</t>
+          <t>60874</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89351</t>
+          <t>89812</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140612</t>
+          <t>143818</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>186282</t>
+          <t>184958</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109649</t>
+          <t>108975</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>145312</t>
+          <t>145393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77962</t>
+          <t>78145</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108213</t>
+          <t>107941</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>195562</t>
+          <t>192986</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>243770</t>
+          <t>241718</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23878</t>
+          <t>25269</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24198</t>
+          <t>25146</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21634</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44207</t>
+          <t>42007</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23664</t>
+          <t>23615</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46605</t>
+          <t>45683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21565</t>
+          <t>21224</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41696</t>
+          <t>42111</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49101</t>
+          <t>49766</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>80660</t>
+          <t>80128</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85486</t>
+          <t>84967</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>121037</t>
+          <t>120665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52346</t>
+          <t>53984</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81197</t>
+          <t>81381</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>146326</t>
+          <t>147574</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>192284</t>
+          <t>192847</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>114820</t>
+          <t>115629</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>155488</t>
+          <t>154511</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61248</t>
+          <t>63688</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91839</t>
+          <t>93443</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>187680</t>
+          <t>186679</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>237772</t>
+          <t>237357</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154116</t>
+          <t>156234</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>198165</t>
+          <t>197623</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>110419</t>
+          <t>111022</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>144175</t>
+          <t>146279</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>276004</t>
+          <t>277218</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>329931</t>
+          <t>333990</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,98%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>10572</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28351</t>
+          <t>28167</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>13007</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29912</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26825</t>
+          <t>28681</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51851</t>
+          <t>53826</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>20228</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43488</t>
+          <t>42673</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18129</t>
+          <t>17872</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39253</t>
+          <t>37625</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43314</t>
+          <t>43834</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>72657</t>
+          <t>77607</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55281</t>
+          <t>56434</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>87019</t>
+          <t>87865</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>34884</t>
+          <t>34668</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>60231</t>
+          <t>59227</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>97112</t>
+          <t>97196</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>138001</t>
+          <t>136661</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>90693</t>
+          <t>90414</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126878</t>
+          <t>127403</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59682</t>
+          <t>58723</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88114</t>
+          <t>88643</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>159409</t>
+          <t>160593</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>203933</t>
+          <t>210509</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>34,46%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>122313</t>
+          <t>121046</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>162307</t>
+          <t>160006</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>62433</t>
+          <t>61424</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>91987</t>
+          <t>91597</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>193366</t>
+          <t>191799</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>241473</t>
+          <t>242009</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17604</t>
+          <t>18173</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>16319</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28354</t>
+          <t>28517</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22177</t>
+          <t>22299</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14466</t>
+          <t>15122</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13178</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31967</t>
+          <t>31087</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30618</t>
+          <t>30608</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>53869</t>
+          <t>54504</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16696</t>
+          <t>16815</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>35701</t>
+          <t>33663</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>51966</t>
+          <t>52075</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>82740</t>
+          <t>82334</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24275</t>
+          <t>24195</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>45882</t>
+          <t>46044</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19997</t>
+          <t>18688</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>39791</t>
+          <t>38764</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>48567</t>
+          <t>47467</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>78052</t>
+          <t>78738</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>53274</t>
+          <t>52745</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>79406</t>
+          <t>79419</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>24692</t>
+          <t>27241</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>46913</t>
+          <t>48325</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>87455</t>
+          <t>86729</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>121786</t>
+          <t>121755</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,83%</t>
         </is>
       </c>
     </row>
@@ -9832,97 +9832,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9945,97 +9945,97 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>62,38%</t>
         </is>
       </c>
     </row>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>904</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>68,69%</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>8335</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -10514,97 +10514,97 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10627,97 +10627,97 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10740,97 +10740,97 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10853,97 +10853,97 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10966,97 +10966,97 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
           <t>795</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>53024</t>
+          <t>51619</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>85565</t>
+          <t>86108</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>44422</t>
+          <t>43798</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>74051</t>
+          <t>74665</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>104357</t>
+          <t>105542</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>149534</t>
+          <t>150354</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>102562</t>
+          <t>102552</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>148351</t>
+          <t>146198</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>84348</t>
+          <t>83913</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>122642</t>
+          <t>120147</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,47 +11359,47 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>11,58%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>225454</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>200005</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>256263</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
           <t>8,13%</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>11,82%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>225454</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>198031</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>256569</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>279019</t>
+          <t>277644</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>340812</t>
+          <t>342219</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>202914</t>
+          <t>204091</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>256265</t>
+          <t>257401</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>496863</t>
+          <t>501122</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>579647</t>
+          <t>587496</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>359026</t>
+          <t>359690</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>426156</t>
+          <t>425206</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>250976</t>
+          <t>251409</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>306827</t>
+          <t>310178</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>629701</t>
+          <t>626956</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>719610</t>
+          <t>720969</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>493187</t>
+          <t>494012</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>566456</t>
+          <t>566863</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>339872</t>
+          <t>338875</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>395734</t>
+          <t>398800</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>849429</t>
+          <t>847458</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>946415</t>
+          <t>945711</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6712-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6712-Edad-trans_orig.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>941</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10478</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15699</t>
+          <t>14883</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8779</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23640</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7618</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21879</t>
+          <t>21712</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19670</t>
+          <t>19117</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40332</t>
+          <t>38737</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12789</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28615</t>
+          <t>28653</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15871</t>
+          <t>16152</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33370</t>
+          <t>32378</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33266</t>
+          <t>32862</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57966</t>
+          <t>55897</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30215</t>
+          <t>29663</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48517</t>
+          <t>48214</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33959</t>
+          <t>34359</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52573</t>
+          <t>53301</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68278</t>
+          <t>70528</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95301</t>
+          <t>96076</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,26%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13661</t>
+          <t>13052</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31242</t>
+          <t>30871</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>9400</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26241</t>
+          <t>26026</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>26656</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50657</t>
+          <t>52850</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28830</t>
+          <t>28703</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16341</t>
+          <t>17506</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16645</t>
+          <t>16846</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>37340</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48133</t>
+          <t>48420</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78079</t>
+          <t>77265</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28909</t>
+          <t>28259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52827</t>
+          <t>52611</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>84337</t>
+          <t>83250</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120984</t>
+          <t>119992</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75848</t>
+          <t>75209</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108869</t>
+          <t>108985</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55008</t>
+          <t>56833</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85599</t>
+          <t>84280</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140719</t>
+          <t>139427</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>183655</t>
+          <t>183796</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>173093</t>
+          <t>171504</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>211948</t>
+          <t>212292</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121063</t>
+          <t>119333</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155707</t>
+          <t>155336</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>304806</t>
+          <t>305202</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>355990</t>
+          <t>354523</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,98%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22876</t>
+          <t>23276</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14900</t>
+          <t>14567</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>13452</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31927</t>
+          <t>31550</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12292</t>
+          <t>12505</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31610</t>
+          <t>31287</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22680</t>
+          <t>22342</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23365</t>
+          <t>22174</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48383</t>
+          <t>45763</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57985</t>
+          <t>58379</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>88644</t>
+          <t>90254</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48221</t>
+          <t>47542</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>76821</t>
+          <t>77773</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>114023</t>
+          <t>110912</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>155583</t>
+          <t>155627</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89651</t>
+          <t>89358</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124129</t>
+          <t>123260</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59103</t>
+          <t>59435</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87800</t>
+          <t>88945</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>155962</t>
+          <t>155589</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>201317</t>
+          <t>201659</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>192449</t>
+          <t>191642</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>234236</t>
+          <t>232784</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>112624</t>
+          <t>113341</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>147382</t>
+          <t>147068</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>317447</t>
+          <t>317221</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>369261</t>
+          <t>371186</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,28%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28083</t>
+          <t>28239</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6398</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>20625</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19498</t>
+          <t>18934</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41391</t>
+          <t>41223</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23678</t>
+          <t>23229</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20566</t>
+          <t>21333</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>16748</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>38079</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>38064</t>
+          <t>39009</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67644</t>
+          <t>66455</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26280</t>
+          <t>26084</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51560</t>
+          <t>51398</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>73542</t>
+          <t>70676</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>112300</t>
+          <t>108912</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70345</t>
+          <t>73988</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>106684</t>
+          <t>109247</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46605</t>
+          <t>45398</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>76180</t>
+          <t>76040</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>124003</t>
+          <t>129076</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>170450</t>
+          <t>172777</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>174268</t>
+          <t>175829</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>215449</t>
+          <t>216629</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>88579</t>
+          <t>88048</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>119421</t>
+          <t>119589</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>273102</t>
+          <t>273921</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>326732</t>
+          <t>324620</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>54,94%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14156</t>
+          <t>14356</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17415</t>
+          <t>16990</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15160</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>969</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18082</t>
+          <t>17901</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14891</t>
+          <t>14636</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33781</t>
+          <t>33203</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19673</t>
+          <t>19290</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>24582</t>
+          <t>24772</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>47010</t>
+          <t>48252</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21029</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>42281</t>
+          <t>40813</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9883</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>25886</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>35430</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>63565</t>
+          <t>61338</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>76415</t>
+          <t>76120</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>101910</t>
+          <t>101738</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25721</t>
+          <t>26537</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>43730</t>
+          <t>44171</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>107954</t>
+          <t>107851</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>139328</t>
+          <t>141072</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>62,42%</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>997</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>45490</t>
+          <t>46437</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>75840</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>31526</t>
+          <t>31560</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>58312</t>
+          <t>57718</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>84245</t>
+          <t>83713</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>125607</t>
+          <t>123935</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>50751</t>
+          <t>52442</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>85568</t>
+          <t>86036</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>28139</t>
+          <t>28651</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>55068</t>
+          <t>54074</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>85882</t>
+          <t>88348</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>129736</t>
+          <t>129942</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>197806</t>
+          <t>196914</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>253934</t>
+          <t>252250</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>139050</t>
+          <t>141465</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>187434</t>
+          <t>188814</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>348875</t>
+          <t>347921</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>420571</t>
+          <t>425094</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>303730</t>
+          <t>302679</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>370714</t>
+          <t>367110</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>214922</t>
+          <t>218695</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>270920</t>
+          <t>274046</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>535360</t>
+          <t>538478</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>622905</t>
+          <t>626723</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>690323</t>
+          <t>692765</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>768325</t>
+          <t>769119</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>420656</t>
+          <t>419379</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>484486</t>
+          <t>482649</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1131288</t>
+          <t>1131563</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1235484</t>
+          <t>1236458</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,45%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>10792</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>6759</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20981</t>
+          <t>19867</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>18414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16237</t>
+          <t>16705</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34328</t>
+          <t>33668</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10551</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25910</t>
+          <t>26116</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13927</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30084</t>
+          <t>30209</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28841</t>
+          <t>28586</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51036</t>
+          <t>49309</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>17595</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35143</t>
+          <t>34575</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16978</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33360</t>
+          <t>33371</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38516</t>
+          <t>39038</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62416</t>
+          <t>64091</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>11512</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26909</t>
+          <t>26510</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24774</t>
+          <t>23877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42028</t>
+          <t>42581</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>40126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64411</t>
+          <t>62988</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12731</t>
+          <t>12575</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30844</t>
+          <t>31380</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18201</t>
+          <t>18691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22481</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44540</t>
+          <t>45156</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23791</t>
+          <t>23951</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46528</t>
+          <t>46660</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17156</t>
+          <t>17517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35907</t>
+          <t>36014</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44874</t>
+          <t>46296</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73817</t>
+          <t>77717</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59864</t>
+          <t>60935</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90396</t>
+          <t>92645</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58417</t>
+          <t>57085</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87467</t>
+          <t>85372</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>128357</t>
+          <t>125485</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>169407</t>
+          <t>166900</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72895</t>
+          <t>73630</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106100</t>
+          <t>106058</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60874</t>
+          <t>61225</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89812</t>
+          <t>90010</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>143818</t>
+          <t>142806</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>184958</t>
+          <t>187413</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108975</t>
+          <t>108893</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>145393</t>
+          <t>144765</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78145</t>
+          <t>76036</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107941</t>
+          <t>107954</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>192986</t>
+          <t>193649</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>241718</t>
+          <t>239215</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,71%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25269</t>
+          <t>23190</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9547</t>
+          <t>9283</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25146</t>
+          <t>24995</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>21645</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42007</t>
+          <t>44733</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23615</t>
+          <t>22690</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45683</t>
+          <t>45638</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21224</t>
+          <t>22490</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42111</t>
+          <t>43073</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49766</t>
+          <t>49679</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>80128</t>
+          <t>78454</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84967</t>
+          <t>84169</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>120665</t>
+          <t>120971</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53984</t>
+          <t>53258</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81381</t>
+          <t>80451</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>147574</t>
+          <t>147634</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>192847</t>
+          <t>194204</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>115629</t>
+          <t>115773</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>154511</t>
+          <t>154863</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63688</t>
+          <t>61400</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>93443</t>
+          <t>89419</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>186679</t>
+          <t>188251</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>237357</t>
+          <t>236821</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>156234</t>
+          <t>153347</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>197623</t>
+          <t>196948</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>111022</t>
+          <t>110562</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>146279</t>
+          <t>145382</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>277218</t>
+          <t>278279</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>333990</t>
+          <t>333616</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,94%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10572</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28167</t>
+          <t>29559</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13007</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30268</t>
+          <t>31279</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28681</t>
+          <t>27764</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53826</t>
+          <t>53220</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20228</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42673</t>
+          <t>42403</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17872</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37625</t>
+          <t>37299</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43834</t>
+          <t>43799</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>77607</t>
+          <t>73910</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56434</t>
+          <t>55031</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>87865</t>
+          <t>87000</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>34668</t>
+          <t>34491</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59227</t>
+          <t>59855</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>97196</t>
+          <t>97305</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>136661</t>
+          <t>136788</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>90414</t>
+          <t>92470</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>127403</t>
+          <t>128880</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58723</t>
+          <t>59052</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88643</t>
+          <t>89803</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>160593</t>
+          <t>160612</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>210509</t>
+          <t>208032</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>121046</t>
+          <t>119389</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>160006</t>
+          <t>159364</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>61424</t>
+          <t>62630</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>91597</t>
+          <t>93533</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>191799</t>
+          <t>190334</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>242009</t>
+          <t>241164</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18173</t>
+          <t>17940</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16319</t>
+          <t>15365</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>10481</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28517</t>
+          <t>27992</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22299</t>
+          <t>22216</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15122</t>
+          <t>14135</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>13090</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31087</t>
+          <t>32285</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30608</t>
+          <t>29974</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>54504</t>
+          <t>54574</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>15773</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>33663</t>
+          <t>35730</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>52075</t>
+          <t>53080</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>82334</t>
+          <t>82278</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24195</t>
+          <t>23305</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>46044</t>
+          <t>45713</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>18688</t>
+          <t>20248</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>38764</t>
+          <t>39598</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>47467</t>
+          <t>47871</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>78738</t>
+          <t>79033</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>52745</t>
+          <t>53594</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>79419</t>
+          <t>79211</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>27241</t>
+          <t>26597</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>48325</t>
+          <t>47794</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>86729</t>
+          <t>87382</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>121755</t>
+          <t>121304</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,28%</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>60,3%</t>
         </is>
       </c>
     </row>
@@ -10284,7 +10284,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>8335</t>
+          <t>8351</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,44%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>51619</t>
+          <t>54016</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>86108</t>
+          <t>88525</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>43798</t>
+          <t>45010</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>74665</t>
+          <t>74000</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>105542</t>
+          <t>104826</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>150354</t>
+          <t>147456</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>102552</t>
+          <t>103918</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>146198</t>
+          <t>144669</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>83913</t>
+          <t>83523</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>120147</t>
+          <t>121457</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>200005</t>
+          <t>197916</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>256263</t>
+          <t>255823</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>277644</t>
+          <t>275076</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>342219</t>
+          <t>341572</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>204091</t>
+          <t>204281</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>257401</t>
+          <t>255659</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>501122</t>
+          <t>497493</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>587496</t>
+          <t>579444</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>359690</t>
+          <t>359997</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>425206</t>
+          <t>422348</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>251409</t>
+          <t>250287</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>310178</t>
+          <t>308100</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>626956</t>
+          <t>625388</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>720969</t>
+          <t>713647</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>494012</t>
+          <t>494847</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>566863</t>
+          <t>567744</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>338875</t>
+          <t>338261</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>398800</t>
+          <t>399826</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>847458</t>
+          <t>848788</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>945711</t>
+          <t>951257</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
